--- a/_system/data/scores/2026-06-09.xlsx
+++ b/_system/data/scores/2026-06-09.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="Q1" s="2" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-09 18:49</t>
+          <t>生成时间: 2026-06-09 19:30</t>
         </is>
       </c>
     </row>
@@ -1123,31 +1123,31 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>301611</t>
+          <t>600110</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>珂玛科技</t>
+          <t>诺德股份</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>113</v>
+        <v>11.81</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>10.7843</v>
+        <v>9.9628</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>13.1189</v>
+        <v>5.9086</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>170.4259</v>
+        <v/>
       </c>
       <c r="H12" s="3" t="n">
-        <v>27.5749</v>
+        <v>3.6339</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>92.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>39.4</v>
+        <v>17.7</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>30.4</v>
+        <v>42.7</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>50</v>
@@ -1181,31 +1181,31 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>600110</t>
+          <t>301611</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>诺德股份</t>
+          <t>珂玛科技</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>11.81</v>
+        <v>113</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>9.9628</v>
+        <v>10.7843</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>5.9086</v>
+        <v>13.1189</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v/>
+        <v>170.4259</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>3.6339</v>
+        <v>27.5749</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>17.7</v>
+        <v>39.4</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>42.7</v>
+        <v>30.4</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>50</v>
@@ -2689,45 +2689,45 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>002600</t>
+          <t>301396</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>领益智造</t>
+          <t>宏景科技</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>14.86</v>
+        <v>166</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>3.6262</v>
+        <v>4.3828</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2.5896</v>
+        <v>7.6446</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>47.4707</v>
+        <v>1348.9804</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>4.4786</v>
+        <v>29.547</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>54.9</v>
+        <v>62.2</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>7.8</v>
+        <v>22.9</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>34.9</v>
+        <v>21.3</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>50</v>
@@ -2747,45 +2747,45 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>301396</t>
+          <t>002600</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>宏景科技</t>
+          <t>领益智造</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>166</v>
+        <v>14.86</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>4.3828</v>
+        <v>3.6262</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>7.6446</v>
+        <v>2.5896</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1348.9804</v>
+        <v>47.4707</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>29.547</v>
+        <v>4.4786</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>62.2</v>
+        <v>54.9</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>22.9</v>
+        <v>7.8</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>21.3</v>
+        <v>34.9</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>50</v>
@@ -3153,45 +3153,45 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>002261</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>拓维信息</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>443.92</v>
+        <v>28.1</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>4.4247</v>
+        <v>3.8817</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>4.512</v>
+        <v>4.7203</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>171.4623</v>
+        <v>555.4356</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>57.5308</v>
+        <v>13.5963</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>63.4</v>
+        <v>58.5</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>13.5</v>
+        <v>14.2</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>15.1</v>
+        <v>20.9</v>
       </c>
       <c r="N47" s="3" t="n">
         <v>50</v>
@@ -3211,45 +3211,45 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>002261</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>拓维信息</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>28.1</v>
+        <v>443.92</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.8817</v>
+        <v>4.4247</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4.7203</v>
+        <v>4.512</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>555.4356</v>
+        <v>171.4623</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>13.5963</v>
+        <v>57.5308</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>58.5</v>
+        <v>63.4</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>14.2</v>
+        <v>13.5</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>20.9</v>
+        <v>15.1</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>50</v>
@@ -3849,45 +3849,45 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>600170</t>
+          <t>002195</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>上海建工</t>
+          <t>岩山科技</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>2.44</v>
+        <v>7.31</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>0</v>
+        <v>2.2378</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>1.07</v>
+        <v>2.247</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>17.5257</v>
+        <v>449.3285</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.6926</v>
+        <v>4.1889</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>19.5</v>
+        <v>35.4</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>50</v>
+        <v>61.2</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>3.2</v>
+        <v>6.7</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>52.5</v>
+        <v>30.6</v>
       </c>
       <c r="N59" s="3" t="n">
         <v>50</v>
@@ -3907,45 +3907,45 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>002195</t>
+          <t>600170</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>岩山科技</t>
+          <t>上海建工</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>7.31</v>
+        <v>2.44</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>2.2378</v>
+        <v>0</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>2.247</v>
+        <v>1.07</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>449.3285</v>
+        <v>17.5257</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>4.1889</v>
+        <v>0.6926</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>35.4</v>
+        <v>19.5</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>61.2</v>
+        <v>50</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>6.7</v>
+        <v>3.2</v>
       </c>
       <c r="M60" s="3" t="n">
-        <v>30.6</v>
+        <v>52.5</v>
       </c>
       <c r="N60" s="3" t="n">
         <v>50</v>
